--- a/artfynd/A 17619-2023 artfynd.xlsx
+++ b/artfynd/A 17619-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 17619-2023 artfynd.xlsx
+++ b/artfynd/A 17619-2023 artfynd.xlsx
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>104946976</v>
+        <v>104947287</v>
       </c>
       <c r="B2" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>81312</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>1049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>434747.7074779588</v>
+        <v>434747</v>
       </c>
       <c r="R2" t="n">
-        <v>6670894.438656708</v>
+        <v>6670896</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,21 +743,11 @@
           <t>2022-05-17</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-06-29</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -771,6 +756,11 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>silverved av tall</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -787,37 +777,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>104947318</v>
+        <v>104946976</v>
       </c>
       <c r="B3" t="n">
-        <v>8377</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>434749.7278106898</v>
+        <v>434747</v>
       </c>
       <c r="R3" t="n">
-        <v>6670895.895977724</v>
+        <v>6670895</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,26 +845,11 @@
           <t>2022-05-17</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-06-29</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>gamla gnagspår</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -888,11 +858,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>torrtall</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -912,16 +877,11 @@
         <v>104947124</v>
       </c>
       <c r="B4" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -949,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>434721.6884543815</v>
+        <v>434722</v>
       </c>
       <c r="R4" t="n">
-        <v>6670805.303147687</v>
+        <v>6670806</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -982,19 +942,9 @@
           <t>2022-05-17</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-06-29</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,37 +971,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>104947360</v>
+        <v>104947318</v>
       </c>
       <c r="B5" t="n">
-        <v>77259</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8455</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1061,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>434729.1876010764</v>
+        <v>434749</v>
       </c>
       <c r="R5" t="n">
-        <v>6670862.413574404</v>
+        <v>6670896</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1094,19 +1039,14 @@
           <t>2022-05-17</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-06-29</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>gamla gnagspår</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1120,7 +1060,7 @@
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>brandstubbe</t>
+          <t>torrtall</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1138,15 +1078,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>104947287</v>
+        <v>104947360</v>
       </c>
       <c r="B6" t="n">
-        <v>79433</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1154,21 +1089,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1049</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1178,10 +1113,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>434747.7251998224</v>
+        <v>434729</v>
       </c>
       <c r="R6" t="n">
-        <v>6670895.433872309</v>
+        <v>6670862</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1211,21 +1146,11 @@
           <t>2022-05-17</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-06-29</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1237,7 +1162,7 @@
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>silverved av tall</t>
+          <t>brandstubbe</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>

--- a/artfynd/A 17619-2023 artfynd.xlsx
+++ b/artfynd/A 17619-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104947287</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -871,6 +881,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104946976</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -968,6 +983,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104947124</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1075,6 +1095,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104947318</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,8 +1202,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104947360</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>